--- a/Design-Files/Smart_Connect_Board/Deliverables/BOM/Client-BOM-Smart_Connect_Board.xlsx
+++ b/Design-Files/Smart_Connect_Board/Deliverables/BOM/Client-BOM-Smart_Connect_Board.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="358">
   <si>
     <t>#</t>
   </si>
@@ -1312,9 +1312,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1329,6 +1326,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1641,9 +1641,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2167,28 +2167,28 @@
       <c r="C18" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="I18" s="16" t="s">
+      <c r="I18" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="14">
         <v>2</v>
       </c>
-      <c r="K18" s="17" t="s">
+      <c r="K18" s="16" t="s">
         <v>356</v>
       </c>
     </row>
@@ -2777,26 +2777,30 @@
       <c r="C37" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="17" t="s">
         <v>354</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="G37" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="H37" s="7"/>
-      <c r="I37" s="8" t="s">
+      <c r="H37" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="J37" s="7">
+      <c r="I37" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="J37" s="17">
         <v>1</v>
       </c>
-      <c r="K37" s="7"/>
+      <c r="K37" s="16" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
@@ -3127,28 +3131,28 @@
       <c r="C48" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="E48" s="16" t="s">
+      <c r="E48" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="F48" s="15" t="s">
+      <c r="F48" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="G48" s="16" t="s">
+      <c r="G48" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H48" s="15" t="s">
+      <c r="H48" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="I48" s="16" t="s">
+      <c r="I48" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="J48" s="15">
+      <c r="J48" s="14">
         <v>3</v>
       </c>
-      <c r="K48" s="17" t="s">
+      <c r="K48" s="16" t="s">
         <v>356</v>
       </c>
     </row>
@@ -3865,28 +3869,28 @@
       <c r="C71" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D71" s="18" t="s">
+      <c r="D71" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E71" s="19" t="s">
+      <c r="E71" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="F71" s="18" t="s">
+      <c r="F71" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="G71" s="19" t="s">
+      <c r="G71" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="H71" s="18" t="s">
+      <c r="H71" s="17" t="s">
         <v>288</v>
       </c>
-      <c r="I71" s="19" t="s">
+      <c r="I71" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="J71" s="18">
+      <c r="J71" s="17">
         <v>2</v>
       </c>
-      <c r="K71" s="17" t="s">
+      <c r="K71" s="16" t="s">
         <v>356</v>
       </c>
     </row>
@@ -3899,28 +3903,28 @@
       <c r="C72" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D72" s="15" t="s">
+      <c r="D72" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E72" s="16" t="s">
+      <c r="E72" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="F72" s="15" t="s">
+      <c r="F72" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="G72" s="16" t="s">
+      <c r="G72" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="H72" s="15" t="s">
+      <c r="H72" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="I72" s="16" t="s">
+      <c r="I72" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="J72" s="15">
+      <c r="J72" s="14">
         <v>2</v>
       </c>
-      <c r="K72" s="17" t="s">
+      <c r="K72" s="16" t="s">
         <v>356</v>
       </c>
     </row>
